--- a/public/Bulk_PeopleEnrichment_Template.xlsx
+++ b/public/Bulk_PeopleEnrichment_Template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_Personal\04_Dusseldorf_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{536315EC-8985-4458-AE8C-F64915D496AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639A1F1A-64D5-4BF2-B1A7-ED8EEE42C425}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8010" xr2:uid="{7213B884-E8D1-4EF1-B0FF-D858765345BA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Main_Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/public/Bulk_PeopleEnrichment_Template.xlsx
+++ b/public/Bulk_PeopleEnrichment_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_Personal\04_Dusseldorf_Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shah\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639A1F1A-64D5-4BF2-B1A7-ED8EEE42C425}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2345E1A3-ABF2-40F8-B1F4-C1B531186041}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8010" xr2:uid="{7213B884-E8D1-4EF1-B0FF-D858765345BA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7830" xr2:uid="{7213B884-E8D1-4EF1-B0FF-D858765345BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main_Data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Sr No</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>LinkedIn URL</t>
+  </si>
+  <si>
+    <t>Record Id</t>
   </si>
 </sst>
 </file>
@@ -426,29 +429,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAE05F2-4D5D-4CDE-A7AC-063C2693E024}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" customWidth="1"/>
-    <col min="4" max="4" width="26.7265625" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/public/Bulk_PeopleEnrichment_Template.xlsx
+++ b/public/Bulk_PeopleEnrichment_Template.xlsx
@@ -5,12 +5,13 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shah\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_Personal\04_Dusseldorf_Project\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2345E1A3-ABF2-40F8-B1F4-C1B531186041}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECC6D11-89DC-4704-9522-07E07C2CC7CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="EM/umyW/reIh+DZyT8tDiTdreMu0N/YWLC4Rn4LByzlb9GZNEYm53fTqhV3HmPBxdm+QfjfOqunoclv3vOrhgg==" workbookSaltValue="7Zfz1fQ0SQqJuMh3ggUoIw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7830" xr2:uid="{7213B884-E8D1-4EF1-B0FF-D858765345BA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{7213B884-E8D1-4EF1-B0FF-D858765345BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main_Data" sheetId="1" r:id="rId1"/>
@@ -66,7 +67,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -79,8 +80,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -89,16 +96,95 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -107,9 +193,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -429,37 +536,1142 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAE05F2-4D5D-4CDE-A7AC-063C2693E024}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="4"/>
+    <col min="2" max="2" width="14.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="4"/>
+    <col min="8" max="8" width="15.140625" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="11.42578125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="str">
+        <f>IF(COUNTA(B2:F2)&gt;0, ROW()-1, "")</f>
+        <v/>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="str">
+        <f t="shared" ref="A3:A66" si="0">IF(COUNTA(B3:F3)&gt;0, ROW()-1, "")</f>
+        <v/>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="7"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="7"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="7"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="7"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="7"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="7"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="7"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="7"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="7"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="7"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="7"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="7"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="7"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="str">
+        <f t="shared" ref="A67:A100" si="1">IF(COUNTA(B67:F67)&gt;0, ROW()-1, "")</f>
+        <v/>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="7"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="7"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="7"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="7"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="7"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="7"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="7"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="7"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="7"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="7"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="7"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="7"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="7"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="7"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="7"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="7"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="7"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="7"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="7"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="7"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="7"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="7"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="7"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="7"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="7"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="7"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="7"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="7"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="7"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="7"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="7"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="7"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="7"/>
+    </row>
+    <row r="101" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="8" t="str">
+        <f>IF(COUNTA(B101:F101)&gt;0, ROW()-1, "")</f>
+        <v/>
+      </c>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="10"/>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="t77K/o61QXSAk3Dwr7RcMlatypPgrksUccVA15ueH3PD+PB94zC4WMwezmX0tGcRkunKxy2GoMChJvN4M5qpfw==" saltValue="CjSBUKYtb37h0mXb2p+DYg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatColumns="0" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/public/Bulk_PeopleEnrichment_Template.xlsx
+++ b/public/Bulk_PeopleEnrichment_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_Personal\04_Dusseldorf_Project\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_Personal\04_Dusseldorf_Project\InputFiles\PeopleEnrichment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECC6D11-89DC-4704-9522-07E07C2CC7CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD27B6F0-48F0-40F1-A25F-8D007D38C9FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="EM/umyW/reIh+DZyT8tDiTdreMu0N/YWLC4Rn4LByzlb9GZNEYm53fTqhV3HmPBxdm+QfjfOqunoclv3vOrhgg==" workbookSaltValue="7Zfz1fQ0SQqJuMh3ggUoIw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{7213B884-E8D1-4EF1-B0FF-D858765345BA}"/>
@@ -571,10 +571,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="str">
-        <f>IF(COUNTA(B2:F2)&gt;0, ROW()-1, "")</f>
-        <v/>
-      </c>
+      <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -582,10 +579,7 @@
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="str">
-        <f t="shared" ref="A3:A66" si="0">IF(COUNTA(B3:F3)&gt;0, ROW()-1, "")</f>
-        <v/>
-      </c>
+      <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -593,10 +587,7 @@
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -604,10 +595,7 @@
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -615,10 +603,7 @@
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -626,10 +611,7 @@
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -637,10 +619,7 @@
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -648,10 +627,7 @@
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -659,10 +635,7 @@
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -670,10 +643,7 @@
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -681,10 +651,7 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -692,10 +659,7 @@
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -703,10 +667,7 @@
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -714,10 +675,7 @@
       <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -725,10 +683,7 @@
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -736,10 +691,7 @@
       <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -747,10 +699,7 @@
       <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -758,10 +707,7 @@
       <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -769,10 +715,7 @@
       <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -780,10 +723,7 @@
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -791,10 +731,7 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -802,10 +739,7 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -813,10 +747,7 @@
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -824,10 +755,7 @@
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -835,10 +763,7 @@
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -846,10 +771,7 @@
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -857,10 +779,7 @@
       <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -868,10 +787,7 @@
       <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -879,10 +795,7 @@
       <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -890,10 +803,7 @@
       <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -901,10 +811,7 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A32" s="5"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -912,10 +819,7 @@
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A33" s="5"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
@@ -923,10 +827,7 @@
       <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A34" s="5"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -934,10 +835,7 @@
       <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A35" s="5"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -945,10 +843,7 @@
       <c r="F35" s="7"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A36" s="5"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
@@ -956,10 +851,7 @@
       <c r="F36" s="7"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A37" s="5"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -967,10 +859,7 @@
       <c r="F37" s="7"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A38" s="5"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -978,10 +867,7 @@
       <c r="F38" s="7"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A39" s="5"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
@@ -989,10 +875,7 @@
       <c r="F39" s="7"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A40" s="5"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
@@ -1000,10 +883,7 @@
       <c r="F40" s="7"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A41" s="5"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
@@ -1011,10 +891,7 @@
       <c r="F41" s="7"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A42" s="5"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
@@ -1022,10 +899,7 @@
       <c r="F42" s="7"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A43" s="5"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
@@ -1033,10 +907,7 @@
       <c r="F43" s="7"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A44" s="5"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
@@ -1044,10 +915,7 @@
       <c r="F44" s="7"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A45" s="5"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
@@ -1055,10 +923,7 @@
       <c r="F45" s="7"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A46" s="5"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
@@ -1066,10 +931,7 @@
       <c r="F46" s="7"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A47" s="5"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
@@ -1077,10 +939,7 @@
       <c r="F47" s="7"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A48" s="5"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
@@ -1088,10 +947,7 @@
       <c r="F48" s="7"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A49" s="5"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
@@ -1099,10 +955,7 @@
       <c r="F49" s="7"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A50" s="5"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -1110,10 +963,7 @@
       <c r="F50" s="7"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A51" s="5"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1121,10 +971,7 @@
       <c r="F51" s="7"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A52" s="5"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -1132,10 +979,7 @@
       <c r="F52" s="7"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A53" s="5"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -1143,10 +987,7 @@
       <c r="F53" s="7"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A54" s="5"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
@@ -1154,10 +995,7 @@
       <c r="F54" s="7"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A55" s="5"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
@@ -1165,10 +1003,7 @@
       <c r="F55" s="7"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A56" s="5"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -1176,10 +1011,7 @@
       <c r="F56" s="7"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A57" s="5"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -1187,10 +1019,7 @@
       <c r="F57" s="7"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A58" s="5"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
@@ -1198,10 +1027,7 @@
       <c r="F58" s="7"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A59" s="5"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -1209,10 +1035,7 @@
       <c r="F59" s="7"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A60" s="5"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
@@ -1220,10 +1043,7 @@
       <c r="F60" s="7"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A61" s="5"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
@@ -1231,10 +1051,7 @@
       <c r="F61" s="7"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A62" s="5"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -1242,10 +1059,7 @@
       <c r="F62" s="7"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A63" s="5"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -1253,10 +1067,7 @@
       <c r="F63" s="7"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A64" s="5"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -1264,10 +1075,7 @@
       <c r="F64" s="7"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A65" s="5"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -1275,10 +1083,7 @@
       <c r="F65" s="7"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="A66" s="5"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
@@ -1286,10 +1091,7 @@
       <c r="F66" s="7"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="str">
-        <f t="shared" ref="A67:A100" si="1">IF(COUNTA(B67:F67)&gt;0, ROW()-1, "")</f>
-        <v/>
-      </c>
+      <c r="A67" s="5"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
@@ -1297,10 +1099,7 @@
       <c r="F67" s="7"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A68" s="5"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -1308,10 +1107,7 @@
       <c r="F68" s="7"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A69" s="5"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
@@ -1319,10 +1115,7 @@
       <c r="F69" s="7"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A70" s="5"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
@@ -1330,10 +1123,7 @@
       <c r="F70" s="7"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A71" s="5"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
@@ -1341,10 +1131,7 @@
       <c r="F71" s="7"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A72" s="5"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
@@ -1352,10 +1139,7 @@
       <c r="F72" s="7"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A73" s="5"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
@@ -1363,10 +1147,7 @@
       <c r="F73" s="7"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A74" s="5"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
@@ -1374,10 +1155,7 @@
       <c r="F74" s="7"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A75" s="5"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
@@ -1385,10 +1163,7 @@
       <c r="F75" s="7"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A76" s="5"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
@@ -1396,10 +1171,7 @@
       <c r="F76" s="7"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A77" s="5"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
       <c r="D77" s="6"/>
@@ -1407,10 +1179,7 @@
       <c r="F77" s="7"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A78" s="5"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
@@ -1418,10 +1187,7 @@
       <c r="F78" s="7"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A79" s="5"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
@@ -1429,10 +1195,7 @@
       <c r="F79" s="7"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A80" s="5"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
@@ -1440,10 +1203,7 @@
       <c r="F80" s="7"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A81" s="5"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
@@ -1451,10 +1211,7 @@
       <c r="F81" s="7"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A82" s="5"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
@@ -1462,10 +1219,7 @@
       <c r="F82" s="7"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A83" s="5"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
@@ -1473,10 +1227,7 @@
       <c r="F83" s="7"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A84" s="5"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
       <c r="D84" s="6"/>
@@ -1484,10 +1235,7 @@
       <c r="F84" s="7"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A85" s="5"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
@@ -1495,10 +1243,7 @@
       <c r="F85" s="7"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A86" s="5"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
@@ -1506,10 +1251,7 @@
       <c r="F86" s="7"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A87" s="5"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
       <c r="D87" s="6"/>
@@ -1517,10 +1259,7 @@
       <c r="F87" s="7"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A88" s="5"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
@@ -1528,10 +1267,7 @@
       <c r="F88" s="7"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A89" s="5"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
       <c r="D89" s="6"/>
@@ -1539,10 +1275,7 @@
       <c r="F89" s="7"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A90" s="5"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
@@ -1550,10 +1283,7 @@
       <c r="F90" s="7"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A91" s="5"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
@@ -1561,10 +1291,7 @@
       <c r="F91" s="7"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A92" s="5"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
       <c r="D92" s="6"/>
@@ -1572,10 +1299,7 @@
       <c r="F92" s="7"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A93" s="5"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
       <c r="D93" s="6"/>
@@ -1583,10 +1307,7 @@
       <c r="F93" s="7"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A94" s="5"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
@@ -1594,10 +1315,7 @@
       <c r="F94" s="7"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A95" s="5"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
       <c r="D95" s="6"/>
@@ -1605,10 +1323,7 @@
       <c r="F95" s="7"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A96" s="5"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
       <c r="D96" s="6"/>
@@ -1616,10 +1331,7 @@
       <c r="F96" s="7"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A97" s="5"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
@@ -1627,10 +1339,7 @@
       <c r="F97" s="7"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A98" s="5"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
@@ -1638,10 +1347,7 @@
       <c r="F98" s="7"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A99" s="5"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
@@ -1649,10 +1355,7 @@
       <c r="F99" s="7"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A100" s="5"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
@@ -1660,10 +1363,7 @@
       <c r="F100" s="7"/>
     </row>
     <row r="101" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8" t="str">
-        <f>IF(COUNTA(B101:F101)&gt;0, ROW()-1, "")</f>
-        <v/>
-      </c>
+      <c r="A101" s="8"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
